--- a/tools/importer/reports/import-careers-centre-page.report.xlsx
+++ b/tools/importer/reports/import-careers-centre-page.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="346">
   <si>
     <t>_reportFile</t>
   </si>
@@ -37,21 +37,861 @@
     <t>url</t>
   </si>
   <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-aberdeen.report.json</t>
+  </si>
+  <si>
+    <t>["columns-location"]</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-aberdeen</t>
+  </si>
+  <si>
+    <t>success</t>
+  </si>
+  <si>
+    <t>careers-centre-page</t>
+  </si>
+  <si>
+    <t>2026-03-10T17:58:38.375Z</t>
+  </si>
+  <si>
+    <t>AFCO Aberdeen</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/armed-forces-careers-office-aberdeen/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-belfast.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-belfast</t>
+  </si>
+  <si>
+    <t>2026-03-10T17:59:15.483Z</t>
+  </si>
+  <si>
+    <t>ACC Belfast</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/armed-forces-careers-office-belfast/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-bloomsbury-wc1.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-bloomsbury-wc1</t>
+  </si>
+  <si>
+    <t>2026-03-10T17:59:52.007Z</t>
+  </si>
+  <si>
+    <t>AFCO London Handle Street</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/armed-forces-careers-office-bloomsbury-wc1/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-bournemouth.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-bournemouth</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:00:28.861Z</t>
+  </si>
+  <si>
+    <t>AFCO Bournemouth</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/armed-forces-careers-office-bournemouth/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-brighton.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-brighton</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:01:06.506Z</t>
+  </si>
+  <si>
+    <t>AFCO Brighton</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/armed-forces-careers-office-brighton/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-bristol.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-bristol</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:01:43.017Z</t>
+  </si>
+  <si>
+    <t>AFCO Bristol</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/armed-forces-careers-office-bristol/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-cambridge.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-cambridge</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:02:19.666Z</t>
+  </si>
+  <si>
+    <t>AFCO Cambridge</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/armed-forces-careers-office-cambridge/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-carlisle.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-carlisle</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:02:56.595Z</t>
+  </si>
+  <si>
+    <t>AFCO Carlisle</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/armed-forces-careers-office-carlisle/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-chatham.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-chatham</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:03:33.385Z</t>
+  </si>
+  <si>
+    <t>AFCO Chatham</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/armed-forces-careers-office-chatham/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-dundee.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-dundee</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:04:09.477Z</t>
+  </si>
+  <si>
+    <t>AFCO Dundee</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/armed-forces-careers-office-dundee/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-edinburgh.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-edinburgh</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:04:46.162Z</t>
+  </si>
+  <si>
+    <t>AFCO Edinburgh</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/armed-forces-careers-office-edinburgh/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-exeter.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-exeter</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:05:23.359Z</t>
+  </si>
+  <si>
+    <t>AFCO Exeter</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/armed-forces-careers-office-exeter/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-glasgow.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-glasgow</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:06:00.218Z</t>
+  </si>
+  <si>
+    <t>AFCO Glasgow</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/armed-forces-careers-office-glasgow/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-hull.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-hull</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:06:36.461Z</t>
+  </si>
+  <si>
+    <t>ACC Hull</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/armed-forces-careers-office-hull/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-inverness.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-inverness</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:07:13.033Z</t>
+  </si>
+  <si>
+    <t>AFCO Inverness</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/armed-forces-careers-office-inverness/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-leeds.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-leeds</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:07:50.444Z</t>
+  </si>
+  <si>
+    <t>AFCO Leeds</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/armed-forces-careers-office-leeds/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-leicester.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-leicester</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:09:17.238Z</t>
+  </si>
+  <si>
+    <t>AFCO Leicester</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/armed-forces-careers-office-leicester/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-lincoln.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-lincoln</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:10:26.100Z</t>
+  </si>
+  <si>
+    <t>AFCO Lincoln</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/armed-forces-careers-office-lincoln/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-liverpool.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-liverpool</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:11:34.765Z</t>
+  </si>
+  <si>
+    <t>AFCO Liverpool</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/armed-forces-careers-office-liverpool/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-manchester.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-manchester</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:12:41.616Z</t>
+  </si>
+  <si>
+    <t>AFCO Manchester</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/armed-forces-careers-office-manchester/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-middlesbrough.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-middlesbrough</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:13:49.592Z</t>
+  </si>
+  <si>
+    <t>AFCO Middlesbrough</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/armed-forces-careers-office-middlesbrough/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-newcastle-upon-tyne.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-newcastle-upon-tyne</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:14:28.348Z</t>
+  </si>
+  <si>
+    <t>AFCO Newcastle</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/armed-forces-careers-office-newcastle-upon-tyne/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-norwich.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-norwich</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:15:04.551Z</t>
+  </si>
+  <si>
+    <t>AFCO Norwich</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/armed-forces-careers-office-norwich/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-nottingham.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-nottingham</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:15:41.013Z</t>
+  </si>
+  <si>
+    <t>AFCO Nottingham</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/armed-forces-careers-office-nottingham/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-peterborough.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-peterborough</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:16:18.476Z</t>
+  </si>
+  <si>
+    <t>AFCO Peterborough</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/armed-forces-careers-office-peterborough/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-plymouth.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-plymouth</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:16:54.693Z</t>
+  </si>
+  <si>
+    <t>AFCO Plymouth</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/armed-forces-careers-office-plymouth/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-portsmouth.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-portsmouth</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:17:30.957Z</t>
+  </si>
+  <si>
+    <t>AFCO Portsmouth</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/armed-forces-careers-office-portsmouth/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-preston.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-preston</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:18:06.814Z</t>
+  </si>
+  <si>
+    <t>AFCO Preston</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/armed-forces-careers-office-preston/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-reading.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-reading</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:18:42.593Z</t>
+  </si>
+  <si>
+    <t>AFCO Reading</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/armed-forces-careers-office-reading/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-redruth.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-redruth</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:19:40.165Z</t>
+  </si>
+  <si>
+    <t>AFCO Redruth</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/armed-forces-careers-office-redruth/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-sheffield.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-sheffield</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:20:47.763Z</t>
+  </si>
+  <si>
+    <t>AFCO Sheffield</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/armed-forces-careers-office-sheffield/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-shrewsbury.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-shrewsbury</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:21:55.487Z</t>
+  </si>
+  <si>
+    <t>AFCO Shrewsbury</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/armed-forces-careers-office-shrewsbury/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-stoke-on-trent.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-stoke-on-trent</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:23:04.048Z</t>
+  </si>
+  <si>
+    <t>AFCO Stoke-on-Trent</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/armed-forces-careers-office-stoke-on-trent/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-wrexham.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/armed-forces-careers-office-wrexham</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:24:12.134Z</t>
+  </si>
+  <si>
+    <t>Wrexham AFCO</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/armed-forces-careers-office-wrexham/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-centre-bangor.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-centre-bangor</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:24:51.983Z</t>
+  </si>
+  <si>
+    <t>ACC Bangor</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/army-careers-centre-bangor/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-centre-birmingham.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-centre-birmingham</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:25:29.230Z</t>
+  </si>
+  <si>
+    <t>ACC Birmingham</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/army-careers-centre-birmingham/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-centre-bolton.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-centre-bolton</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:26:05.644Z</t>
+  </si>
+  <si>
+    <t>ACC Bolton</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/army-careers-centre-bolton/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-centre-bradford.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-centre-bradford</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:26:41.886Z</t>
+  </si>
+  <si>
+    <t>ACC Bradford</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/army-careers-centre-bradford/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-centre-canterbury.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-centre-canterbury</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:27:19.083Z</t>
+  </si>
+  <si>
+    <t>ACC Canterbury</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/army-careers-centre-canterbury/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-centre-cardiff.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-centre-cardiff</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:27:54.314Z</t>
+  </si>
+  <si>
+    <t>ACC Cardiff</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/army-careers-centre-cardiff/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-centre-chelmsford.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-centre-chelmsford</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:28:30.358Z</t>
+  </si>
+  <si>
+    <t>ACC Chelmsford</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/army-careers-centre-chelmsford/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-centre-coleraine.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-centre-coleraine</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:30:34.739Z</t>
+  </si>
+  <si>
+    <t>ACC Coleraine</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/army-careers-centre-coleraine/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-centre-coventry.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-centre-coventry</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:31:12.984Z</t>
+  </si>
+  <si>
+    <t>ACC Coventry</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/army-careers-centre-coventry/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-centre-crawley.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-centre-crawley</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:31:49.058Z</t>
+  </si>
+  <si>
+    <t>Mobile ACC - Crawley Area</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/army-careers-centre-crawley/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-centre-derby.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-centre-derby</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:32:24.715Z</t>
+  </si>
+  <si>
+    <t>Mobile ACC - Derby Area</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/army-careers-centre-derby/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-centre-doncaster.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-centre-doncaster</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:33:01.710Z</t>
+  </si>
+  <si>
+    <t>ACC Doncaster</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/army-careers-centre-doncaster/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-centre-enniskillen.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-centre-enniskillen</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:33:37.402Z</t>
+  </si>
+  <si>
+    <t>ACC Enniskillen</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/army-careers-centre-enniskillen/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-centre-hereford.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-centre-hereford</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:34:12.414Z</t>
+  </si>
+  <si>
+    <t>Mobile ACC - Hereford Area</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/army-careers-centre-hereford/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-centre-milton-keynes.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-centre-milton-keynes</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:34:48.296Z</t>
+  </si>
+  <si>
+    <t>Mobile ACC - Milton Keynes</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/army-careers-centre-milton-keynes/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-centre-northampton.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-centre-northampton</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:35:23.513Z</t>
+  </si>
+  <si>
+    <t>ACC Northampton</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/army-careers-centre-northampton/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-centre-oxford.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-centre-oxford</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:35:59.802Z</t>
+  </si>
+  <si>
+    <t>ACC Oxford</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/army-careers-centre-oxford/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-centre-portadown.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-centre-portadown</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:36:36.490Z</t>
+  </si>
+  <si>
+    <t>ACC Portadown</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/army-careers-centre-portadown/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-centre-reserve-centre-luton.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-centre-reserve-centre-luton</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:37:14.207Z</t>
+  </si>
+  <si>
+    <t>ACC Luton</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/army-careers-centre-reserve-centre-luton/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-centre-salisbury.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-centre-salisbury</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:37:49.588Z</t>
+  </si>
+  <si>
+    <t>ACC Salisbury</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/army-careers-centre-salisbury/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-centre-southampton.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-centre-southampton</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:38:26.835Z</t>
+  </si>
+  <si>
+    <t>Mobile ACC - Southampton</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/army-careers-centre-southampton/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-centre-swansea.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-centre-swansea</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:39:03.706Z</t>
+  </si>
+  <si>
+    <t>ACC Swansea</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/army-careers-centre-swansea/</t>
+  </si>
+  <si>
     <t>army-careers-centre-finder/army-careers-centre-swindon.report.json</t>
   </si>
   <si>
-    <t>["columns-location"]</t>
-  </si>
-  <si>
     <t>army-careers-centre-finder/army-careers-centre-swindon</t>
   </si>
   <si>
-    <t>success</t>
-  </si>
-  <si>
-    <t>careers-centre-page</t>
-  </si>
-  <si>
     <t>2026-03-09T19:42:21.361Z</t>
   </si>
   <si>
@@ -59,6 +899,156 @@
   </si>
   <si>
     <t>https://jobs.army.mod.uk/army-careers-centre-finder/army-careers-centre-swindon/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-centre-taunton.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-centre-taunton</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:39:41.003Z</t>
+  </si>
+  <si>
+    <t>ACC Taunton</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/army-careers-centre-taunton/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-centre-victoria-sw1.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-centre-victoria-sw1</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:40:59.906Z</t>
+  </si>
+  <si>
+    <t>Mobile ACC London Victoria</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/army-careers-centre-victoria-sw1/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-centre-wolverhampton.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-centre-wolverhampton</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:41:35.853Z</t>
+  </si>
+  <si>
+    <t>ACC Wolverhampton</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/army-careers-centre-wolverhampton/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-centre-worcester.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-centre-worcester</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:42:12.404Z</t>
+  </si>
+  <si>
+    <t>ACC Worcester</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/army-careers-centre-worcester/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-centre-york.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-centre-york</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:42:49.186Z</t>
+  </si>
+  <si>
+    <t>ACC York</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/army-careers-centre-york/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-office-aldershot.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-office-aldershot</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:43:25.297Z</t>
+  </si>
+  <si>
+    <t>ACC Aldershot</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/army-careers-office-aldershot/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-office-chester.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-office-chester</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:44:02.601Z</t>
+  </si>
+  <si>
+    <t>ACC Chester</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/army-careers-office-chester/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-office-gloucester.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-office-gloucester</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:44:39.163Z</t>
+  </si>
+  <si>
+    <t>ACC Gloucester</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/army-careers-office-gloucester/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-office-ipswich.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-office-ipswich</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:45:16.580Z</t>
+  </si>
+  <si>
+    <t>Mobile ACC - Ipswich Area</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/army-careers-office-ipswich/</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-office-stockport.report.json</t>
+  </si>
+  <si>
+    <t>army-careers-centre-finder/army-careers-office-stockport</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:45:52.750Z</t>
+  </si>
+  <si>
+    <t>Mobile ACC - Stockport</t>
+  </si>
+  <si>
+    <t>https://jobs.army.mod.uk/army-careers-centre-finder/army-careers-office-stockport/</t>
   </si>
 </sst>
 </file>
@@ -447,7 +1437,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -455,7 +1445,7 @@
     <col min="3" max="3" width="50" customWidth="1"/>
     <col min="5" max="5" width="21" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="13" customWidth="1"/>
+    <col min="7" max="7" width="28" customWidth="1"/>
     <col min="8" max="8" width="50" customWidth="1"/>
   </cols>
   <sheetData>
@@ -511,6 +1501,1722 @@
         <v>15</v>
       </c>
     </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G8" t="s">
+        <v>44</v>
+      </c>
+      <c r="H8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" t="s">
+        <v>48</v>
+      </c>
+      <c r="G9" t="s">
+        <v>49</v>
+      </c>
+      <c r="H9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" t="s">
+        <v>53</v>
+      </c>
+      <c r="G10" t="s">
+        <v>54</v>
+      </c>
+      <c r="H10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" t="s">
+        <v>58</v>
+      </c>
+      <c r="G11" t="s">
+        <v>59</v>
+      </c>
+      <c r="H11" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" t="s">
+        <v>63</v>
+      </c>
+      <c r="G12" t="s">
+        <v>64</v>
+      </c>
+      <c r="H12" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>66</v>
+      </c>
+      <c r="B13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" t="s">
+        <v>68</v>
+      </c>
+      <c r="G13" t="s">
+        <v>69</v>
+      </c>
+      <c r="H13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>71</v>
+      </c>
+      <c r="B14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" t="s">
+        <v>72</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" t="s">
+        <v>73</v>
+      </c>
+      <c r="G14" t="s">
+        <v>74</v>
+      </c>
+      <c r="H14" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>76</v>
+      </c>
+      <c r="B15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" t="s">
+        <v>78</v>
+      </c>
+      <c r="G15" t="s">
+        <v>79</v>
+      </c>
+      <c r="H15" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>81</v>
+      </c>
+      <c r="B16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" t="s">
+        <v>82</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" t="s">
+        <v>83</v>
+      </c>
+      <c r="G16" t="s">
+        <v>84</v>
+      </c>
+      <c r="H16" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>86</v>
+      </c>
+      <c r="B17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" t="s">
+        <v>87</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" t="s">
+        <v>88</v>
+      </c>
+      <c r="G17" t="s">
+        <v>89</v>
+      </c>
+      <c r="H17" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>91</v>
+      </c>
+      <c r="B18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" t="s">
+        <v>92</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" t="s">
+        <v>93</v>
+      </c>
+      <c r="G18" t="s">
+        <v>94</v>
+      </c>
+      <c r="H18" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>96</v>
+      </c>
+      <c r="B19" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" t="s">
+        <v>97</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" t="s">
+        <v>98</v>
+      </c>
+      <c r="G19" t="s">
+        <v>99</v>
+      </c>
+      <c r="H19" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>101</v>
+      </c>
+      <c r="B20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" t="s">
+        <v>102</v>
+      </c>
+      <c r="D20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" t="s">
+        <v>103</v>
+      </c>
+      <c r="G20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H20" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>106</v>
+      </c>
+      <c r="B21" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" t="s">
+        <v>107</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" t="s">
+        <v>108</v>
+      </c>
+      <c r="G21" t="s">
+        <v>109</v>
+      </c>
+      <c r="H21" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>111</v>
+      </c>
+      <c r="B22" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" t="s">
+        <v>112</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" t="s">
+        <v>113</v>
+      </c>
+      <c r="G22" t="s">
+        <v>114</v>
+      </c>
+      <c r="H22" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>116</v>
+      </c>
+      <c r="B23" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" t="s">
+        <v>117</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" t="s">
+        <v>118</v>
+      </c>
+      <c r="G23" t="s">
+        <v>119</v>
+      </c>
+      <c r="H23" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>121</v>
+      </c>
+      <c r="B24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" t="s">
+        <v>122</v>
+      </c>
+      <c r="D24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" t="s">
+        <v>123</v>
+      </c>
+      <c r="G24" t="s">
+        <v>124</v>
+      </c>
+      <c r="H24" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>126</v>
+      </c>
+      <c r="B25" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" t="s">
+        <v>127</v>
+      </c>
+      <c r="D25" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" t="s">
+        <v>128</v>
+      </c>
+      <c r="G25" t="s">
+        <v>129</v>
+      </c>
+      <c r="H25" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>131</v>
+      </c>
+      <c r="B26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" t="s">
+        <v>132</v>
+      </c>
+      <c r="D26" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" t="s">
+        <v>133</v>
+      </c>
+      <c r="G26" t="s">
+        <v>134</v>
+      </c>
+      <c r="H26" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>136</v>
+      </c>
+      <c r="B27" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" t="s">
+        <v>137</v>
+      </c>
+      <c r="D27" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27" t="s">
+        <v>138</v>
+      </c>
+      <c r="G27" t="s">
+        <v>139</v>
+      </c>
+      <c r="H27" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>141</v>
+      </c>
+      <c r="B28" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" t="s">
+        <v>142</v>
+      </c>
+      <c r="D28" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28" t="s">
+        <v>143</v>
+      </c>
+      <c r="G28" t="s">
+        <v>144</v>
+      </c>
+      <c r="H28" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>146</v>
+      </c>
+      <c r="B29" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29" t="s">
+        <v>147</v>
+      </c>
+      <c r="D29" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29" t="s">
+        <v>148</v>
+      </c>
+      <c r="G29" t="s">
+        <v>149</v>
+      </c>
+      <c r="H29" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>151</v>
+      </c>
+      <c r="B30" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" t="s">
+        <v>152</v>
+      </c>
+      <c r="D30" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" t="s">
+        <v>12</v>
+      </c>
+      <c r="F30" t="s">
+        <v>153</v>
+      </c>
+      <c r="G30" t="s">
+        <v>154</v>
+      </c>
+      <c r="H30" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>156</v>
+      </c>
+      <c r="B31" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" t="s">
+        <v>157</v>
+      </c>
+      <c r="D31" t="s">
+        <v>11</v>
+      </c>
+      <c r="E31" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31" t="s">
+        <v>158</v>
+      </c>
+      <c r="G31" t="s">
+        <v>159</v>
+      </c>
+      <c r="H31" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>161</v>
+      </c>
+      <c r="B32" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" t="s">
+        <v>162</v>
+      </c>
+      <c r="D32" t="s">
+        <v>11</v>
+      </c>
+      <c r="E32" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32" t="s">
+        <v>163</v>
+      </c>
+      <c r="G32" t="s">
+        <v>164</v>
+      </c>
+      <c r="H32" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>166</v>
+      </c>
+      <c r="B33" t="s">
+        <v>9</v>
+      </c>
+      <c r="C33" t="s">
+        <v>167</v>
+      </c>
+      <c r="D33" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" t="s">
+        <v>12</v>
+      </c>
+      <c r="F33" t="s">
+        <v>168</v>
+      </c>
+      <c r="G33" t="s">
+        <v>169</v>
+      </c>
+      <c r="H33" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>171</v>
+      </c>
+      <c r="B34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C34" t="s">
+        <v>172</v>
+      </c>
+      <c r="D34" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34" t="s">
+        <v>173</v>
+      </c>
+      <c r="G34" t="s">
+        <v>174</v>
+      </c>
+      <c r="H34" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>176</v>
+      </c>
+      <c r="B35" t="s">
+        <v>9</v>
+      </c>
+      <c r="C35" t="s">
+        <v>177</v>
+      </c>
+      <c r="D35" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" t="s">
+        <v>12</v>
+      </c>
+      <c r="F35" t="s">
+        <v>178</v>
+      </c>
+      <c r="G35" t="s">
+        <v>179</v>
+      </c>
+      <c r="H35" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>181</v>
+      </c>
+      <c r="B36" t="s">
+        <v>9</v>
+      </c>
+      <c r="C36" t="s">
+        <v>182</v>
+      </c>
+      <c r="D36" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" t="s">
+        <v>12</v>
+      </c>
+      <c r="F36" t="s">
+        <v>183</v>
+      </c>
+      <c r="G36" t="s">
+        <v>184</v>
+      </c>
+      <c r="H36" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>186</v>
+      </c>
+      <c r="B37" t="s">
+        <v>9</v>
+      </c>
+      <c r="C37" t="s">
+        <v>187</v>
+      </c>
+      <c r="D37" t="s">
+        <v>11</v>
+      </c>
+      <c r="E37" t="s">
+        <v>12</v>
+      </c>
+      <c r="F37" t="s">
+        <v>188</v>
+      </c>
+      <c r="G37" t="s">
+        <v>189</v>
+      </c>
+      <c r="H37" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>191</v>
+      </c>
+      <c r="B38" t="s">
+        <v>9</v>
+      </c>
+      <c r="C38" t="s">
+        <v>192</v>
+      </c>
+      <c r="D38" t="s">
+        <v>11</v>
+      </c>
+      <c r="E38" t="s">
+        <v>12</v>
+      </c>
+      <c r="F38" t="s">
+        <v>193</v>
+      </c>
+      <c r="G38" t="s">
+        <v>194</v>
+      </c>
+      <c r="H38" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>196</v>
+      </c>
+      <c r="B39" t="s">
+        <v>9</v>
+      </c>
+      <c r="C39" t="s">
+        <v>197</v>
+      </c>
+      <c r="D39" t="s">
+        <v>11</v>
+      </c>
+      <c r="E39" t="s">
+        <v>12</v>
+      </c>
+      <c r="F39" t="s">
+        <v>198</v>
+      </c>
+      <c r="G39" t="s">
+        <v>199</v>
+      </c>
+      <c r="H39" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>201</v>
+      </c>
+      <c r="B40" t="s">
+        <v>9</v>
+      </c>
+      <c r="C40" t="s">
+        <v>202</v>
+      </c>
+      <c r="D40" t="s">
+        <v>11</v>
+      </c>
+      <c r="E40" t="s">
+        <v>12</v>
+      </c>
+      <c r="F40" t="s">
+        <v>203</v>
+      </c>
+      <c r="G40" t="s">
+        <v>204</v>
+      </c>
+      <c r="H40" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>206</v>
+      </c>
+      <c r="B41" t="s">
+        <v>9</v>
+      </c>
+      <c r="C41" t="s">
+        <v>207</v>
+      </c>
+      <c r="D41" t="s">
+        <v>11</v>
+      </c>
+      <c r="E41" t="s">
+        <v>12</v>
+      </c>
+      <c r="F41" t="s">
+        <v>208</v>
+      </c>
+      <c r="G41" t="s">
+        <v>209</v>
+      </c>
+      <c r="H41" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>211</v>
+      </c>
+      <c r="B42" t="s">
+        <v>9</v>
+      </c>
+      <c r="C42" t="s">
+        <v>212</v>
+      </c>
+      <c r="D42" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" t="s">
+        <v>12</v>
+      </c>
+      <c r="F42" t="s">
+        <v>213</v>
+      </c>
+      <c r="G42" t="s">
+        <v>214</v>
+      </c>
+      <c r="H42" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>216</v>
+      </c>
+      <c r="B43" t="s">
+        <v>9</v>
+      </c>
+      <c r="C43" t="s">
+        <v>217</v>
+      </c>
+      <c r="D43" t="s">
+        <v>11</v>
+      </c>
+      <c r="E43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F43" t="s">
+        <v>218</v>
+      </c>
+      <c r="G43" t="s">
+        <v>219</v>
+      </c>
+      <c r="H43" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>221</v>
+      </c>
+      <c r="B44" t="s">
+        <v>9</v>
+      </c>
+      <c r="C44" t="s">
+        <v>222</v>
+      </c>
+      <c r="D44" t="s">
+        <v>11</v>
+      </c>
+      <c r="E44" t="s">
+        <v>12</v>
+      </c>
+      <c r="F44" t="s">
+        <v>223</v>
+      </c>
+      <c r="G44" t="s">
+        <v>224</v>
+      </c>
+      <c r="H44" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>226</v>
+      </c>
+      <c r="B45" t="s">
+        <v>9</v>
+      </c>
+      <c r="C45" t="s">
+        <v>227</v>
+      </c>
+      <c r="D45" t="s">
+        <v>11</v>
+      </c>
+      <c r="E45" t="s">
+        <v>12</v>
+      </c>
+      <c r="F45" t="s">
+        <v>228</v>
+      </c>
+      <c r="G45" t="s">
+        <v>229</v>
+      </c>
+      <c r="H45" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>231</v>
+      </c>
+      <c r="B46" t="s">
+        <v>9</v>
+      </c>
+      <c r="C46" t="s">
+        <v>232</v>
+      </c>
+      <c r="D46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E46" t="s">
+        <v>12</v>
+      </c>
+      <c r="F46" t="s">
+        <v>233</v>
+      </c>
+      <c r="G46" t="s">
+        <v>234</v>
+      </c>
+      <c r="H46" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>236</v>
+      </c>
+      <c r="B47" t="s">
+        <v>9</v>
+      </c>
+      <c r="C47" t="s">
+        <v>237</v>
+      </c>
+      <c r="D47" t="s">
+        <v>11</v>
+      </c>
+      <c r="E47" t="s">
+        <v>12</v>
+      </c>
+      <c r="F47" t="s">
+        <v>238</v>
+      </c>
+      <c r="G47" t="s">
+        <v>239</v>
+      </c>
+      <c r="H47" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>241</v>
+      </c>
+      <c r="B48" t="s">
+        <v>9</v>
+      </c>
+      <c r="C48" t="s">
+        <v>242</v>
+      </c>
+      <c r="D48" t="s">
+        <v>11</v>
+      </c>
+      <c r="E48" t="s">
+        <v>12</v>
+      </c>
+      <c r="F48" t="s">
+        <v>243</v>
+      </c>
+      <c r="G48" t="s">
+        <v>244</v>
+      </c>
+      <c r="H48" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>246</v>
+      </c>
+      <c r="B49" t="s">
+        <v>9</v>
+      </c>
+      <c r="C49" t="s">
+        <v>247</v>
+      </c>
+      <c r="D49" t="s">
+        <v>11</v>
+      </c>
+      <c r="E49" t="s">
+        <v>12</v>
+      </c>
+      <c r="F49" t="s">
+        <v>248</v>
+      </c>
+      <c r="G49" t="s">
+        <v>249</v>
+      </c>
+      <c r="H49" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>251</v>
+      </c>
+      <c r="B50" t="s">
+        <v>9</v>
+      </c>
+      <c r="C50" t="s">
+        <v>252</v>
+      </c>
+      <c r="D50" t="s">
+        <v>11</v>
+      </c>
+      <c r="E50" t="s">
+        <v>12</v>
+      </c>
+      <c r="F50" t="s">
+        <v>253</v>
+      </c>
+      <c r="G50" t="s">
+        <v>254</v>
+      </c>
+      <c r="H50" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>256</v>
+      </c>
+      <c r="B51" t="s">
+        <v>9</v>
+      </c>
+      <c r="C51" t="s">
+        <v>257</v>
+      </c>
+      <c r="D51" t="s">
+        <v>11</v>
+      </c>
+      <c r="E51" t="s">
+        <v>12</v>
+      </c>
+      <c r="F51" t="s">
+        <v>258</v>
+      </c>
+      <c r="G51" t="s">
+        <v>259</v>
+      </c>
+      <c r="H51" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>261</v>
+      </c>
+      <c r="B52" t="s">
+        <v>9</v>
+      </c>
+      <c r="C52" t="s">
+        <v>262</v>
+      </c>
+      <c r="D52" t="s">
+        <v>11</v>
+      </c>
+      <c r="E52" t="s">
+        <v>12</v>
+      </c>
+      <c r="F52" t="s">
+        <v>263</v>
+      </c>
+      <c r="G52" t="s">
+        <v>264</v>
+      </c>
+      <c r="H52" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>266</v>
+      </c>
+      <c r="B53" t="s">
+        <v>9</v>
+      </c>
+      <c r="C53" t="s">
+        <v>267</v>
+      </c>
+      <c r="D53" t="s">
+        <v>11</v>
+      </c>
+      <c r="E53" t="s">
+        <v>12</v>
+      </c>
+      <c r="F53" t="s">
+        <v>268</v>
+      </c>
+      <c r="G53" t="s">
+        <v>269</v>
+      </c>
+      <c r="H53" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>271</v>
+      </c>
+      <c r="B54" t="s">
+        <v>9</v>
+      </c>
+      <c r="C54" t="s">
+        <v>272</v>
+      </c>
+      <c r="D54" t="s">
+        <v>11</v>
+      </c>
+      <c r="E54" t="s">
+        <v>12</v>
+      </c>
+      <c r="F54" t="s">
+        <v>273</v>
+      </c>
+      <c r="G54" t="s">
+        <v>274</v>
+      </c>
+      <c r="H54" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>276</v>
+      </c>
+      <c r="B55" t="s">
+        <v>9</v>
+      </c>
+      <c r="C55" t="s">
+        <v>277</v>
+      </c>
+      <c r="D55" t="s">
+        <v>11</v>
+      </c>
+      <c r="E55" t="s">
+        <v>12</v>
+      </c>
+      <c r="F55" t="s">
+        <v>278</v>
+      </c>
+      <c r="G55" t="s">
+        <v>279</v>
+      </c>
+      <c r="H55" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>281</v>
+      </c>
+      <c r="B56" t="s">
+        <v>9</v>
+      </c>
+      <c r="C56" t="s">
+        <v>282</v>
+      </c>
+      <c r="D56" t="s">
+        <v>11</v>
+      </c>
+      <c r="E56" t="s">
+        <v>12</v>
+      </c>
+      <c r="F56" t="s">
+        <v>283</v>
+      </c>
+      <c r="G56" t="s">
+        <v>284</v>
+      </c>
+      <c r="H56" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>286</v>
+      </c>
+      <c r="B57" t="s">
+        <v>9</v>
+      </c>
+      <c r="C57" t="s">
+        <v>287</v>
+      </c>
+      <c r="D57" t="s">
+        <v>11</v>
+      </c>
+      <c r="E57" t="s">
+        <v>12</v>
+      </c>
+      <c r="F57" t="s">
+        <v>288</v>
+      </c>
+      <c r="G57" t="s">
+        <v>289</v>
+      </c>
+      <c r="H57" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>291</v>
+      </c>
+      <c r="B58" t="s">
+        <v>9</v>
+      </c>
+      <c r="C58" t="s">
+        <v>292</v>
+      </c>
+      <c r="D58" t="s">
+        <v>11</v>
+      </c>
+      <c r="E58" t="s">
+        <v>12</v>
+      </c>
+      <c r="F58" t="s">
+        <v>293</v>
+      </c>
+      <c r="G58" t="s">
+        <v>294</v>
+      </c>
+      <c r="H58" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>296</v>
+      </c>
+      <c r="B59" t="s">
+        <v>9</v>
+      </c>
+      <c r="C59" t="s">
+        <v>297</v>
+      </c>
+      <c r="D59" t="s">
+        <v>11</v>
+      </c>
+      <c r="E59" t="s">
+        <v>12</v>
+      </c>
+      <c r="F59" t="s">
+        <v>298</v>
+      </c>
+      <c r="G59" t="s">
+        <v>299</v>
+      </c>
+      <c r="H59" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>301</v>
+      </c>
+      <c r="B60" t="s">
+        <v>9</v>
+      </c>
+      <c r="C60" t="s">
+        <v>302</v>
+      </c>
+      <c r="D60" t="s">
+        <v>11</v>
+      </c>
+      <c r="E60" t="s">
+        <v>12</v>
+      </c>
+      <c r="F60" t="s">
+        <v>303</v>
+      </c>
+      <c r="G60" t="s">
+        <v>304</v>
+      </c>
+      <c r="H60" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>306</v>
+      </c>
+      <c r="B61" t="s">
+        <v>9</v>
+      </c>
+      <c r="C61" t="s">
+        <v>307</v>
+      </c>
+      <c r="D61" t="s">
+        <v>11</v>
+      </c>
+      <c r="E61" t="s">
+        <v>12</v>
+      </c>
+      <c r="F61" t="s">
+        <v>308</v>
+      </c>
+      <c r="G61" t="s">
+        <v>309</v>
+      </c>
+      <c r="H61" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>311</v>
+      </c>
+      <c r="B62" t="s">
+        <v>9</v>
+      </c>
+      <c r="C62" t="s">
+        <v>312</v>
+      </c>
+      <c r="D62" t="s">
+        <v>11</v>
+      </c>
+      <c r="E62" t="s">
+        <v>12</v>
+      </c>
+      <c r="F62" t="s">
+        <v>313</v>
+      </c>
+      <c r="G62" t="s">
+        <v>314</v>
+      </c>
+      <c r="H62" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>316</v>
+      </c>
+      <c r="B63" t="s">
+        <v>9</v>
+      </c>
+      <c r="C63" t="s">
+        <v>317</v>
+      </c>
+      <c r="D63" t="s">
+        <v>11</v>
+      </c>
+      <c r="E63" t="s">
+        <v>12</v>
+      </c>
+      <c r="F63" t="s">
+        <v>318</v>
+      </c>
+      <c r="G63" t="s">
+        <v>319</v>
+      </c>
+      <c r="H63" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>321</v>
+      </c>
+      <c r="B64" t="s">
+        <v>9</v>
+      </c>
+      <c r="C64" t="s">
+        <v>322</v>
+      </c>
+      <c r="D64" t="s">
+        <v>11</v>
+      </c>
+      <c r="E64" t="s">
+        <v>12</v>
+      </c>
+      <c r="F64" t="s">
+        <v>323</v>
+      </c>
+      <c r="G64" t="s">
+        <v>324</v>
+      </c>
+      <c r="H64" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>326</v>
+      </c>
+      <c r="B65" t="s">
+        <v>9</v>
+      </c>
+      <c r="C65" t="s">
+        <v>327</v>
+      </c>
+      <c r="D65" t="s">
+        <v>11</v>
+      </c>
+      <c r="E65" t="s">
+        <v>12</v>
+      </c>
+      <c r="F65" t="s">
+        <v>328</v>
+      </c>
+      <c r="G65" t="s">
+        <v>329</v>
+      </c>
+      <c r="H65" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>331</v>
+      </c>
+      <c r="B66" t="s">
+        <v>9</v>
+      </c>
+      <c r="C66" t="s">
+        <v>332</v>
+      </c>
+      <c r="D66" t="s">
+        <v>11</v>
+      </c>
+      <c r="E66" t="s">
+        <v>12</v>
+      </c>
+      <c r="F66" t="s">
+        <v>333</v>
+      </c>
+      <c r="G66" t="s">
+        <v>334</v>
+      </c>
+      <c r="H66" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>336</v>
+      </c>
+      <c r="B67" t="s">
+        <v>9</v>
+      </c>
+      <c r="C67" t="s">
+        <v>337</v>
+      </c>
+      <c r="D67" t="s">
+        <v>11</v>
+      </c>
+      <c r="E67" t="s">
+        <v>12</v>
+      </c>
+      <c r="F67" t="s">
+        <v>338</v>
+      </c>
+      <c r="G67" t="s">
+        <v>339</v>
+      </c>
+      <c r="H67" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>341</v>
+      </c>
+      <c r="B68" t="s">
+        <v>9</v>
+      </c>
+      <c r="C68" t="s">
+        <v>342</v>
+      </c>
+      <c r="D68" t="s">
+        <v>11</v>
+      </c>
+      <c r="E68" t="s">
+        <v>12</v>
+      </c>
+      <c r="F68" t="s">
+        <v>343</v>
+      </c>
+      <c r="G68" t="s">
+        <v>344</v>
+      </c>
+      <c r="H68" t="s">
+        <v>345</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
